--- a/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
+++ b/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
@@ -807,17 +807,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trend Analysis — PRCPTOT (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — PRCPTOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tau=-0.0847, Slope=-1.5311</t>
+          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tau=-0.0847, Slope=-1.5311</t>
+          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -835,17 +835,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Trend Analysis — SDII (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — SDII</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tau=-0.0935, Slope=-0.0104</t>
+          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tau=-0.0935, Slope=-0.0104</t>
+          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -863,17 +863,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Trend Analysis — Rx1day (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — Rx1day</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tau=0.0643, Slope=0.1632</t>
+          <t>Tau=0.0643, Slope=0.1632, P=0.475958</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tau=0.0643, Slope=0.1632</t>
+          <t>Tau=0.0643, Slope=0.1632, P=0.475958</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -891,17 +891,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trend Analysis — Rx5day (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — Rx5day</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tau=-0.0105, Slope=-0.0435</t>
+          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tau=-0.0105, Slope=-0.0435</t>
+          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -919,17 +919,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Trend Analysis — CDD (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — CDD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tau=0.0503, Slope=0.1212</t>
+          <t>Tau=0.0503, Slope=0.1212, P=0.578214</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tau=0.0503, Slope=0.1212</t>
+          <t>Tau=0.0503, Slope=0.1212, P=0.578214</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -947,17 +947,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trend Analysis — CWD (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — CWD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tau=-0.0526, Slope=0.0000</t>
+          <t>Tau=-0.0526, Slope=0.0000, P=0.556118</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tau=-0.0526, Slope=-0.0000</t>
+          <t>Tau=-0.0526, Slope=-0.0000, P=0.556118</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -975,17 +975,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trend Analysis — R10mm (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — R10mm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tau=-0.0240, Slope=0.0000</t>
+          <t>Tau=-0.0240, Slope=0.0000, P=0.793285</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tau=-0.0240, Slope=-0.0000</t>
+          <t>Tau=-0.0240, Slope=-0.0000, P=0.793285</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1003,17 +1003,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Trend Analysis — R20mm (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — R20mm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tau=-0.0959, Slope=-0.0370</t>
+          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tau=-0.0959, Slope=-0.0370</t>
+          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1031,17 +1031,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Trend Analysis — R50mm (Tau &amp; Slope)</t>
+          <t>Primary Trend (Hamed_Rao_modified_MK) — R50mm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tau=-0.0579, Slope=0.0000</t>
+          <t>Tau=-0.0579, Slope=0.0000, P=0.451230</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tau=-0.0579, Slope=-0.0000</t>
+          <t>Tau=-0.0579, Slope=-0.0000, P=0.451230</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1059,17 +1059,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Trend Analysis — R95p (Tau &amp; Slope)</t>
+          <t>Primary Trend (Ordinary_MK) — R95p</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tau=-0.0678, Slope=-0.7786</t>
+          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tau=-0.0678, Slope=-0.7786</t>
+          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1087,17 +1087,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Trend Analysis — R99p (Tau &amp; Slope)</t>
+          <t>Primary Trend (Hamed_Rao_modified_MK) — R99p</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tau=0.0222, Slope=0.0000</t>
+          <t>Tau=0.0222, Slope=0.0000, P=0.532865</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tau=0.0222, Slope=-0.0000</t>
+          <t>Tau=0.0222, Slope=-0.0000, P=0.532865</t>
         </is>
       </c>
       <c r="D25" t="n">

--- a/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
+++ b/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,17 +807,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — PRCPTOT</t>
+          <t>Primary Test (Ordinary_MK) — PRCPTOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353</t>
+          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353, Z=-0.9417, S=-145.0, VarS=23383.67</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353</t>
+          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353, Z=-0.9417, S=-145.0, VarS=23383.67</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -835,17 +835,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — SDII</t>
+          <t>Primary Test (Ordinary_MK) — SDII</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412</t>
+          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412, Z=-1.0398, S=-160.0, VarS=23380.67</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412</t>
+          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412, Z=-1.0398, S=-160.0, VarS=23380.67</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -863,17 +863,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — Rx1day</t>
+          <t>Primary Test (Ordinary_MK) — Rx1day</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tau=0.0643, Slope=0.1632, P=0.475958</t>
+          <t>Tau=0.0643, Slope=0.1632, P=0.475958, Z=0.7128, S=110.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tau=0.0643, Slope=0.1632, P=0.475958</t>
+          <t>Tau=0.0643, Slope=0.1632, P=0.475958, Z=0.7128, S=110.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -891,17 +891,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — Rx5day</t>
+          <t>Primary Test (Ordinary_MK) — Rx5day</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479</t>
+          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479, Z=-0.1112, S=-18.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479</t>
+          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479, Z=-0.1112, S=-18.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -919,17 +919,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — CDD</t>
+          <t>Primary Test (Ordinary_MK) — CDD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tau=0.0503, Slope=0.1212, P=0.578214</t>
+          <t>Tau=0.0503, Slope=0.1212, P=0.578214, Z=0.5560, S=86.0, VarS=23372.00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tau=0.0503, Slope=0.1212, P=0.578214</t>
+          <t>Tau=0.0503, Slope=0.1212, P=0.578214, Z=0.5560, S=86.0, VarS=23372.00</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -947,17 +947,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — CWD</t>
+          <t>Primary Test (Ordinary_MK) — CWD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tau=-0.0526, Slope=0.0000, P=0.556118</t>
+          <t>Tau=-0.0526, Slope=0.0000, P=0.556118, Z=-0.5886, S=-90.0, VarS=22862.00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tau=-0.0526, Slope=-0.0000, P=0.556118</t>
+          <t>Tau=-0.0526, Slope=-0.0000, P=0.556118, Z=-0.5886, S=-90.0, VarS=22862.00</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -975,17 +975,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — R10mm</t>
+          <t>Primary Test (Ordinary_MK) — R10mm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tau=-0.0240, Slope=0.0000, P=0.793285</t>
+          <t>Tau=-0.0240, Slope=0.0000, P=0.793285, Z=-0.2620, S=-41.0, VarS=23300.33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tau=-0.0240, Slope=-0.0000, P=0.793285</t>
+          <t>Tau=-0.0240, Slope=-0.0000, P=0.793285, Z=-0.2620, S=-41.0, VarS=23300.33</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1003,17 +1003,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — R20mm</t>
+          <t>Primary Test (Ordinary_MK) — R20mm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601</t>
+          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601, Z=-1.0700, S=-164.0, VarS=23204.67</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601</t>
+          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601, Z=-1.0700, S=-164.0, VarS=23204.67</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1031,17 +1031,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Primary Trend (Hamed_Rao_modified_MK) — R50mm</t>
+          <t>Primary Test (Hamed_Rao_modified_MK) — R50mm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tau=-0.0579, Slope=0.0000, P=0.451230</t>
+          <t>Tau=-0.0579, Slope=0.0000, P=0.451230, Z=-0.7534, S=-99.0, VarS=16921.51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tau=-0.0579, Slope=-0.0000, P=0.451230</t>
+          <t>Tau=-0.0579, Slope=-0.0000, P=0.451230, Z=-0.7534, S=-99.0, VarS=16921.51</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1059,17 +1059,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Primary Trend (Ordinary_MK) — R95p</t>
+          <t>Primary Test (Ordinary_MK) — R95p</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017</t>
+          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017, Z=-0.7521, S=-116.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017</t>
+          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017, Z=-0.7521, S=-116.0, VarS=23382.67</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1087,17 +1087,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Primary Trend (Hamed_Rao_modified_MK) — R99p</t>
+          <t>Primary Test (Hamed_Rao_modified_MK) — R99p</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tau=0.0222, Slope=0.0000, P=0.532865</t>
+          <t>Tau=0.0222, Slope=0.0000, P=0.532865, Z=0.6236, S=38.0, VarS=3519.96</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tau=0.0222, Slope=-0.0000, P=0.532865</t>
+          <t>Tau=0.0222, Slope=-0.0000, P=0.532865, Z=0.6236, S=38.0, VarS=3519.96</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1107,6 +1107,34 @@
         <v>0.001</v>
       </c>
       <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BH-FDR Adjusted P-Values (All 11 Indices)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Min FDR P = 0.706706</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Min FDR P = 0.706706</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
+++ b/ETCCDI_ChiangMai/audit/INDEPENDENT_VERIFICATION.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Independent_Verification" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary_Trend_Verification" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_Checks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,60 +414,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Pipeline_Value</t>
+          <t>Primary_Test</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Independent_Value</t>
+          <t>Pipeline_Tau</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Independent_Tau</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Diff_Tau</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>PASS_FAIL</t>
+          <t>Pipeline_S</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Independent_S</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diff_S</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Pipeline_VarS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Independent_VarS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Diff_VarS</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Pipeline_Z</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Independent_Z</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Diff_Z</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pipeline_P</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Independent_P</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Diff_P</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Pipeline_SenSlope</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Independent_SenSlope</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Diff_SenSlope</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Pipeline_CI_low</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Independent_CI_low</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Diff_CI_low</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Pipeline_CI_high</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Independent_CI_high</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Diff_CI_high</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Pipeline_P_FDR</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Independent_P_FDR</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Diff_P_FDR</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P95 Baseline Threshold</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>41.315</v>
+          <t>PRCPTOT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ordinary_MK</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>41.315</v>
+        <v>-0.0847</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.0847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23383.67</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23383.67</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.9417</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.9417</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.346353</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.346353</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-1.5311</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-1.5311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-4.9656</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-4.9656</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.7644</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7644</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -475,22 +670,96 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P99 Baseline Threshold</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>72.889</v>
+          <t>SDII</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ordinary_MK</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>72.889</v>
+        <v>-0.0935</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.0935</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-160</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-160</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23380.67</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23380.67</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1.0398</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.0398</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.298412</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.298412</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -499,26 +768,96 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — PRCPTOT</t>
+          <t>Rx1day</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mean=1153.94</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mean=1153.94</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0643</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.0643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>110</v>
+      </c>
+      <c r="G4" t="n">
+        <v>110</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7128</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7128</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.475958</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.475958</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.2667</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.2667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -527,26 +866,96 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — SDII</t>
+          <t>Rx5day</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mean=12.51</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mean=12.51</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.0105</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.1112</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.1112</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.911479</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.911479</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.6063</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6063</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.911479</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.911479</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -555,26 +964,96 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — Rx1day</t>
+          <t>CDD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mean=82.61</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mean=82.61</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0503</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.0503</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>86</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23372</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23372</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.578214</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.578214</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -583,26 +1062,96 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — Rx5day</t>
+          <t>CWD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mean=141.34</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mean=141.34</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.0526</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22862</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22862</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.5886</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.5886</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.556118</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.556118</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -611,26 +1160,96 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — CDD</t>
+          <t>R10mm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mean=80.90</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Mean=80.90</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.024</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23300.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23300.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.262</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.262</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.793285</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.793285</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.872614</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.872614</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -639,26 +1258,96 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — CWD</t>
+          <t>R20mm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mean=8.71</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Mean=8.71</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.0959</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.0959</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-164</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-164</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23204.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23204.67</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.284601</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.284601</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.1053</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1053</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -667,26 +1356,96 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — R10mm</t>
+          <t>R50mm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mean=36.59</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Mean=36.59</t>
-        </is>
+          <t>Hamed_Rao_modified_MK</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.0579</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.0579</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-99</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-99</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16921.51</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16921.51</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.7534</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.7534</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -695,26 +1454,96 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — R20mm</t>
+          <t>R95p</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mean=17.90</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mean=17.90</t>
-        </is>
+          <t>Ordinary_MK</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.0678</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-116</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23382.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.7521</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.7521</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.452017</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.452017</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.7786</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.7786</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.3837</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3837</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -723,26 +1552,488 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — R50mm</t>
+          <t>R99p</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mean=2.76</t>
+          <t>Hamed_Rao_modified_MK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3519.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3519.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.532865</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.532865</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7067059999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Primary_Test</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pipeline_Value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Independent_Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PASS_FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HF8_Percentile</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P95 Threshold</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>41.315</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.315</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HF8_Percentile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P99 Threshold</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>72.889</v>
+      </c>
+      <c r="E3" t="n">
+        <v>72.889</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PRCPTOT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1153.9441</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1153.9441</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SDII</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.512</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12.512</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rx1day</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>82.61360000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>82.61360000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rx5day</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>141.3407</v>
+      </c>
+      <c r="E7" t="n">
+        <v>141.3407</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>80.89830000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.89830000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CWD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.7119</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.7119</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R10mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>36.5932</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.5932</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R20mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mean Annual Value</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17.8983</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.8983</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R50mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Annual_ETCCDI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mean=2.76</t>
+          <t>Mean Annual Value</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2.7627</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>2.7627</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -751,26 +2042,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — R95p</t>
+          <t>R95p</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mean=274.91</t>
+          <t>Annual_ETCCDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mean=274.91</t>
+          <t>Mean Annual Value</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>274.9051</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F13" t="inlineStr">
+        <v>274.9051</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -779,362 +2073,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETCCDI Annual Series — R99p</t>
+          <t>R99p</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mean=79.54</t>
+          <t>Annual_ETCCDI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mean=79.54</t>
+          <t>Mean Annual Value</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>79.5373</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — PRCPTOT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353, Z=-0.9417, S=-145.0, VarS=23383.67</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tau=-0.0847, Slope=-1.5311, P=0.346353, Z=-0.9417, S=-145.0, VarS=23383.67</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4.6e-05</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — SDII</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412, Z=-1.0398, S=-160.0, VarS=23380.67</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tau=-0.0935, Slope=-0.0104, P=0.298412, Z=-1.0398, S=-160.0, VarS=23380.67</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — Rx1day</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tau=0.0643, Slope=0.1632, P=0.475958, Z=0.7128, S=110.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tau=0.0643, Slope=0.1632, P=0.475958, Z=0.7128, S=110.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4.2e-05</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — Rx5day</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479, Z=-0.1112, S=-18.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tau=-0.0105, Slope=-0.0435, P=0.911479, Z=-0.1112, S=-18.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2.2e-05</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — CDD</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Tau=0.0503, Slope=0.1212, P=0.578214, Z=0.5560, S=86.0, VarS=23372.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tau=0.0503, Slope=0.1212, P=0.578214, Z=0.5560, S=86.0, VarS=23372.00</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3.7e-05</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — CWD</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Tau=-0.0526, Slope=0.0000, P=0.556118, Z=-0.5886, S=-90.0, VarS=22862.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tau=-0.0526, Slope=-0.0000, P=0.556118, Z=-0.5886, S=-90.0, VarS=22862.00</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — R10mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tau=-0.0240, Slope=0.0000, P=0.793285, Z=-0.2620, S=-41.0, VarS=23300.33</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tau=-0.0240, Slope=-0.0000, P=0.793285, Z=-0.2620, S=-41.0, VarS=23300.33</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3.7e-05</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — R20mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601, Z=-1.0700, S=-164.0, VarS=23204.67</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tau=-0.0959, Slope=-0.0370, P=0.284601, Z=-1.0700, S=-164.0, VarS=23204.67</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Primary Test (Hamed_Rao_modified_MK) — R50mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Tau=-0.0579, Slope=0.0000, P=0.451230, Z=-0.7534, S=-99.0, VarS=16921.51</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tau=-0.0579, Slope=-0.0000, P=0.451230, Z=-0.7534, S=-99.0, VarS=16921.51</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3.9e-05</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Primary Test (Ordinary_MK) — R95p</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017, Z=-0.7521, S=-116.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tau=-0.0678, Slope=-0.7786, P=0.452017, Z=-0.7521, S=-116.0, VarS=23382.67</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2.9e-05</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Primary Test (Hamed_Rao_modified_MK) — R99p</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tau=0.0222, Slope=0.0000, P=0.532865, Z=0.6236, S=38.0, VarS=3519.96</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Tau=0.0222, Slope=-0.0000, P=0.532865, Z=0.6236, S=38.0, VarS=3519.96</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>9e-06</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BH-FDR Adjusted P-Values (All 11 Indices)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Min FDR P = 0.706706</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Min FDR P = 0.706706</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F26" t="inlineStr">
+        <v>79.5373</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
